--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/103.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/103.xlsx
@@ -426,13 +426,13 @@
         <v>-25.14466791185648</v>
       </c>
       <c r="E2">
-        <v>-19.64123262294564</v>
+        <v>-16.80489247251446</v>
       </c>
       <c r="F2">
-        <v>-3.738247450559686</v>
+        <v>-2.148884594197761</v>
       </c>
       <c r="G2">
-        <v>-12.83482061503857</v>
+        <v>-13.16652485294558</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-24.71359453384273</v>
       </c>
       <c r="E3">
-        <v>-19.15272775370799</v>
+        <v>-17.97032094916327</v>
       </c>
       <c r="F3">
-        <v>-3.391426586355589</v>
+        <v>-1.875153071044873</v>
       </c>
       <c r="G3">
-        <v>-12.07706766193548</v>
+        <v>-13.10761209587481</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-24.20272351101252</v>
       </c>
       <c r="E4">
-        <v>-20.00248309719055</v>
+        <v>-18.22124551777544</v>
       </c>
       <c r="F4">
-        <v>-3.653002646239797</v>
+        <v>-2.222875198983216</v>
       </c>
       <c r="G4">
-        <v>-11.57861125087718</v>
+        <v>-12.57829146226037</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-23.66584878025056</v>
       </c>
       <c r="E5">
-        <v>-21.05030924196552</v>
+        <v>-18.6139358017493</v>
       </c>
       <c r="F5">
-        <v>-2.70165664718808</v>
+        <v>-2.095833460620272</v>
       </c>
       <c r="G5">
-        <v>-11.23224898746336</v>
+        <v>-12.06911141779406</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-23.10418354926308</v>
       </c>
       <c r="E6">
-        <v>-20.62661108224049</v>
+        <v>-18.89455167812267</v>
       </c>
       <c r="F6">
-        <v>-3.514603990784472</v>
+        <v>-2.114074110829918</v>
       </c>
       <c r="G6">
-        <v>-11.2524509291094</v>
+        <v>-11.50687060025798</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-22.54177591183477</v>
       </c>
       <c r="E7">
-        <v>-22.31228742228262</v>
+        <v>-20.60651369263964</v>
       </c>
       <c r="F7">
-        <v>-3.765229033603672</v>
+        <v>-2.091838244636571</v>
       </c>
       <c r="G7">
-        <v>-10.39802601991427</v>
+        <v>-11.61146747155634</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-21.97834128155874</v>
       </c>
       <c r="E8">
-        <v>-21.03146196897345</v>
+        <v>-20.60585748525032</v>
       </c>
       <c r="F8">
-        <v>-3.583321208683706</v>
+        <v>-1.754701823738603</v>
       </c>
       <c r="G8">
-        <v>-10.50397917302772</v>
+        <v>-10.74372907031883</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-21.4355713697911</v>
       </c>
       <c r="E9">
-        <v>-19.84263429972055</v>
+        <v>-20.75556414066509</v>
       </c>
       <c r="F9">
-        <v>-3.444600318308692</v>
+        <v>-1.985331734189027</v>
       </c>
       <c r="G9">
-        <v>-10.09208460963237</v>
+        <v>-10.71385823607961</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-20.92006821914591</v>
       </c>
       <c r="E10">
-        <v>-22.8832459959521</v>
+        <v>-21.71184104820686</v>
       </c>
       <c r="F10">
-        <v>-3.58584358742523</v>
+        <v>-2.144041958360996</v>
       </c>
       <c r="G10">
-        <v>-9.994377493309951</v>
+        <v>-10.12451397357088</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-20.44876479118238</v>
       </c>
       <c r="E11">
-        <v>-22.04237437149334</v>
+        <v>-22.5119281374558</v>
       </c>
       <c r="F11">
-        <v>-3.307705978056851</v>
+        <v>-1.64680199931955</v>
       </c>
       <c r="G11">
-        <v>-9.056477941930869</v>
+        <v>-9.691418858723392</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-20.03492928814189</v>
       </c>
       <c r="E12">
-        <v>-25.63824550258651</v>
+        <v>-22.49331759750925</v>
       </c>
       <c r="F12">
-        <v>-2.606308245656245</v>
+        <v>-1.754577568628183</v>
       </c>
       <c r="G12">
-        <v>-8.380020964650459</v>
+        <v>-9.07327547263009</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-19.67244867610897</v>
       </c>
       <c r="E13">
-        <v>-26.37381660711557</v>
+        <v>-23.70095100764097</v>
       </c>
       <c r="F13">
-        <v>-3.344208816028614</v>
+        <v>-1.688195518437441</v>
       </c>
       <c r="G13">
-        <v>-8.089587377239766</v>
+        <v>-8.395705012781573</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-19.36308415802786</v>
       </c>
       <c r="E14">
-        <v>-26.17756075917212</v>
+        <v>-24.42726045091566</v>
       </c>
       <c r="F14">
-        <v>-3.0495792400379</v>
+        <v>-1.443236508653391</v>
       </c>
       <c r="G14">
-        <v>-7.360436436504624</v>
+        <v>-8.350052227489071</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-19.08212346322683</v>
       </c>
       <c r="E15">
-        <v>-25.36793789672138</v>
+        <v>-26.06957311151526</v>
       </c>
       <c r="F15">
-        <v>-3.183858424399103</v>
+        <v>-1.062343236437345</v>
       </c>
       <c r="G15">
-        <v>-6.275844368040067</v>
+        <v>-7.845956608113962</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-18.81404399544894</v>
       </c>
       <c r="E16">
-        <v>-27.02898154039595</v>
+        <v>-26.61464887220841</v>
       </c>
       <c r="F16">
-        <v>-2.635700377842377</v>
+        <v>-1.032893118533017</v>
       </c>
       <c r="G16">
-        <v>-8.599525843009786</v>
+        <v>-8.027554780382619</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-18.54320156493799</v>
       </c>
       <c r="E17">
-        <v>-27.59248925294869</v>
+        <v>-27.43430174000862</v>
       </c>
       <c r="F17">
-        <v>-2.431706621228971</v>
+        <v>-0.8453018648624436</v>
       </c>
       <c r="G17">
-        <v>-6.957131222814034</v>
+        <v>-7.452593109826331</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-18.26424897293808</v>
       </c>
       <c r="E18">
-        <v>-27.44847665026026</v>
+        <v>-27.68011370547992</v>
       </c>
       <c r="F18">
-        <v>-2.497371305248888</v>
+        <v>-0.4960422870245049</v>
       </c>
       <c r="G18">
-        <v>-7.995299030959415</v>
+        <v>-7.388334853205261</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-17.98476195445013</v>
       </c>
       <c r="E19">
-        <v>-30.20519766298881</v>
+        <v>-28.36061322784175</v>
       </c>
       <c r="F19">
-        <v>-1.865306267727795</v>
+        <v>-0.3625889849638934</v>
       </c>
       <c r="G19">
-        <v>-6.245306488557815</v>
+        <v>-7.59800636206216</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-17.69950640708679</v>
       </c>
       <c r="E20">
-        <v>-29.94197543564383</v>
+        <v>-28.76871607904205</v>
       </c>
       <c r="F20">
-        <v>-1.560450496149521</v>
+        <v>-0.2283387934617887</v>
       </c>
       <c r="G20">
-        <v>-7.509982497428184</v>
+        <v>-7.116770422326839</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-17.41236528483832</v>
       </c>
       <c r="E21">
-        <v>-31.11509773627189</v>
+        <v>-29.82335349038974</v>
       </c>
       <c r="F21">
-        <v>-2.112087685798004</v>
+        <v>-0.1895098998229647</v>
       </c>
       <c r="G21">
-        <v>-6.851422174319858</v>
+        <v>-7.156884512969294</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-17.11548967063239</v>
       </c>
       <c r="E22">
-        <v>-32.34326046998223</v>
+        <v>-30.32796451314508</v>
       </c>
       <c r="F22">
-        <v>-2.065868098191403</v>
+        <v>-0.03858467250250593</v>
       </c>
       <c r="G22">
-        <v>-7.317693326058917</v>
+        <v>-7.146814871081371</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-16.80954167569375</v>
       </c>
       <c r="E23">
-        <v>-32.36831471729926</v>
+        <v>-30.47430291417542</v>
       </c>
       <c r="F23">
-        <v>-1.593577736954876</v>
+        <v>0.4419338621460285</v>
       </c>
       <c r="G23">
-        <v>-6.710102569602896</v>
+        <v>-7.687323850641032</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-16.49983003336213</v>
       </c>
       <c r="E24">
-        <v>-32.04126386170865</v>
+        <v>-30.08926284546189</v>
       </c>
       <c r="F24">
-        <v>-1.417854503064212</v>
+        <v>0.02523275220916799</v>
       </c>
       <c r="G24">
-        <v>-7.955658790460246</v>
+        <v>-7.684557766746747</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-16.18978839818817</v>
       </c>
       <c r="E25">
-        <v>-31.07483027587201</v>
+        <v>-30.95663818799004</v>
       </c>
       <c r="F25">
-        <v>-2.025919251823994</v>
+        <v>0.2759663111581335</v>
       </c>
       <c r="G25">
-        <v>-8.007205331667187</v>
+        <v>-7.273065258018427</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-15.9010940350892</v>
       </c>
       <c r="E26">
-        <v>-30.58582909788104</v>
+        <v>-30.83440710209468</v>
       </c>
       <c r="F26">
-        <v>-1.710424757691566</v>
+        <v>0.07507396210080865</v>
       </c>
       <c r="G26">
-        <v>-7.446648444392367</v>
+        <v>-8.027798885001889</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-15.64615638103197</v>
       </c>
       <c r="E27">
-        <v>-31.83276434677961</v>
+        <v>-30.22020944532241</v>
       </c>
       <c r="F27">
-        <v>-1.17946693188657</v>
+        <v>0.1239376984571459</v>
       </c>
       <c r="G27">
-        <v>-7.80149040623812</v>
+        <v>-7.92486375263577</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-15.44773888742169</v>
       </c>
       <c r="E28">
-        <v>-31.0265865731228</v>
+        <v>-30.74368850712645</v>
       </c>
       <c r="F28">
-        <v>-1.129391294019937</v>
+        <v>0.3062199454431771</v>
       </c>
       <c r="G28">
-        <v>-7.819052885102539</v>
+        <v>-8.272493532548573</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-15.3174634468344</v>
       </c>
       <c r="E29">
-        <v>-28.80222003479945</v>
+        <v>-30.04534263570183</v>
       </c>
       <c r="F29">
-        <v>-1.933684683359283</v>
+        <v>0.3025651884620257</v>
       </c>
       <c r="G29">
-        <v>-7.986620915938555</v>
+        <v>-7.800027083894801</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-15.2666007567393</v>
       </c>
       <c r="E30">
-        <v>-29.65641100797693</v>
+        <v>-29.86454296370373</v>
       </c>
       <c r="F30">
-        <v>-1.906343588862483</v>
+        <v>0.4792683809902022</v>
       </c>
       <c r="G30">
-        <v>-7.81241637235193</v>
+        <v>-8.172615582098647</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-15.30132567013467</v>
       </c>
       <c r="E31">
-        <v>-30.88868749750452</v>
+        <v>-30.17935222891441</v>
       </c>
       <c r="F31">
-        <v>-2.165012079162865</v>
+        <v>0.1988809257558199</v>
       </c>
       <c r="G31">
-        <v>-8.993981937908798</v>
+        <v>-7.942789124998353</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-15.41460123472786</v>
       </c>
       <c r="E32">
-        <v>-31.15556870402668</v>
+        <v>-29.79769287421929</v>
       </c>
       <c r="F32">
-        <v>-1.3884093553643</v>
+        <v>0.3632679517391734</v>
       </c>
       <c r="G32">
-        <v>-7.948582367246034</v>
+        <v>-8.809496282122369</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-15.60305366235889</v>
       </c>
       <c r="E33">
-        <v>-30.98818598121344</v>
+        <v>-29.15586805571426</v>
       </c>
       <c r="F33">
-        <v>-1.810450949947009</v>
+        <v>0.162224839814539</v>
       </c>
       <c r="G33">
-        <v>-9.497043702425826</v>
+        <v>-8.415729423795412</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-15.84828981604707</v>
       </c>
       <c r="E34">
-        <v>-29.49863466295802</v>
+        <v>-28.78557188720387</v>
       </c>
       <c r="F34">
-        <v>-1.548556796980126</v>
+        <v>0.2055592237571896</v>
       </c>
       <c r="G34">
-        <v>-8.922360076168491</v>
+        <v>-8.307694201870554</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-16.14002082871238</v>
       </c>
       <c r="E35">
-        <v>-29.03541662087158</v>
+        <v>-27.87121957138058</v>
       </c>
       <c r="F35">
-        <v>-1.485753293969479</v>
+        <v>0.1709732279555046</v>
       </c>
       <c r="G35">
-        <v>-7.893093601706512</v>
+        <v>-9.007262795643792</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-16.46018758619266</v>
       </c>
       <c r="E36">
-        <v>-28.76182590145416</v>
+        <v>-27.1216770639548</v>
       </c>
       <c r="F36">
-        <v>-1.485915653980427</v>
+        <v>0.477252963099191</v>
       </c>
       <c r="G36">
-        <v>-8.389269527364478</v>
+        <v>-8.399984023166407</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-16.79179798814283</v>
       </c>
       <c r="E37">
-        <v>-27.48933594327392</v>
+        <v>-27.42417621079868</v>
       </c>
       <c r="F37">
-        <v>-1.155449247409801</v>
+        <v>0.1163705622325724</v>
       </c>
       <c r="G37">
-        <v>-9.212670958583402</v>
+        <v>-8.59532384959039</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-17.12747078302136</v>
       </c>
       <c r="E38">
-        <v>-26.9515573748785</v>
+        <v>-26.27585065838552</v>
       </c>
       <c r="F38">
-        <v>-1.352035742707374</v>
+        <v>0.5644063259151298</v>
       </c>
       <c r="G38">
-        <v>-7.89546807391213</v>
+        <v>-9.100307122126477</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-17.45427567918084</v>
       </c>
       <c r="E39">
-        <v>-26.67143573065279</v>
+        <v>-26.62812188974615</v>
       </c>
       <c r="F39">
-        <v>-1.26317345793946</v>
+        <v>0.4059868587015439</v>
       </c>
       <c r="G39">
-        <v>-8.300992420505166</v>
+        <v>-9.205129822831971</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-17.77351426474215</v>
       </c>
       <c r="E40">
-        <v>-25.89936205178981</v>
+        <v>-25.04199387194883</v>
       </c>
       <c r="F40">
-        <v>-0.5199638808825491</v>
+        <v>0.3007576907891171</v>
       </c>
       <c r="G40">
-        <v>-9.517370959812235</v>
+        <v>-9.121339280552487</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-18.07706597020605</v>
       </c>
       <c r="E41">
-        <v>-26.76975885555678</v>
+        <v>-25.62065665262586</v>
       </c>
       <c r="F41">
-        <v>-1.327293236753156</v>
+        <v>0.6305274403739891</v>
       </c>
       <c r="G41">
-        <v>-8.146586458525247</v>
+        <v>-9.880133920747426</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-18.36933080329655</v>
       </c>
       <c r="E42">
-        <v>-25.77404305327443</v>
+        <v>-24.81688151172047</v>
       </c>
       <c r="F42">
-        <v>-1.606784398457709</v>
+        <v>0.7193715010590417</v>
       </c>
       <c r="G42">
-        <v>-9.756549104037896</v>
+        <v>-9.272763772209352</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-18.65253030528184</v>
       </c>
       <c r="E43">
-        <v>-24.5892066201047</v>
+        <v>-24.3681353344954</v>
       </c>
       <c r="F43">
-        <v>-1.35421517734414</v>
+        <v>0.4598522774359846</v>
       </c>
       <c r="G43">
-        <v>-9.541575172916446</v>
+        <v>-9.432900318566764</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-18.92625025043452</v>
       </c>
       <c r="E44">
-        <v>-25.30661157829896</v>
+        <v>-24.02576535893316</v>
       </c>
       <c r="F44">
-        <v>-1.368833376901342</v>
+        <v>0.5164098902295237</v>
       </c>
       <c r="G44">
-        <v>-8.323829908815929</v>
+        <v>-9.898383025439307</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-19.19734877972095</v>
       </c>
       <c r="E45">
-        <v>-24.65305809101261</v>
+        <v>-22.95635497490306</v>
       </c>
       <c r="F45">
-        <v>-1.551516553710329</v>
+        <v>0.8202948152117167</v>
       </c>
       <c r="G45">
-        <v>-9.389437947986204</v>
+        <v>-10.04533009012241</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-19.46047569255092</v>
       </c>
       <c r="E46">
-        <v>-23.29305581700691</v>
+        <v>-22.37933686591065</v>
       </c>
       <c r="F46">
-        <v>-1.553257781991013</v>
+        <v>0.4594165561821121</v>
       </c>
       <c r="G46">
-        <v>-9.034443257581872</v>
+        <v>-9.618432882934229</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-19.72436996149637</v>
       </c>
       <c r="E47">
-        <v>-22.68104690260282</v>
+        <v>-22.27889145001967</v>
       </c>
       <c r="F47">
-        <v>-1.147199536445321</v>
+        <v>0.5783021890970915</v>
       </c>
       <c r="G47">
-        <v>-9.159287758556614</v>
+        <v>-9.886697332649483</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-19.98762846096804</v>
       </c>
       <c r="E48">
-        <v>-21.51870841517968</v>
+        <v>-21.39465199290705</v>
       </c>
       <c r="F48">
-        <v>-1.754289296772008</v>
+        <v>0.5984464275983699</v>
       </c>
       <c r="G48">
-        <v>-9.732938835328163</v>
+        <v>-10.06766370472709</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-20.24824908490795</v>
       </c>
       <c r="E49">
-        <v>-24.58353748664631</v>
+        <v>-21.15291017453409</v>
       </c>
       <c r="F49">
-        <v>-1.026260380738801</v>
+        <v>0.5264306507011892</v>
       </c>
       <c r="G49">
-        <v>-10.10344918083748</v>
+        <v>-10.80176853332387</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-20.50786690674824</v>
       </c>
       <c r="E50">
-        <v>-22.80560171023443</v>
+        <v>-19.27965404500607</v>
       </c>
       <c r="F50">
-        <v>-1.116302260688302</v>
+        <v>0.3911963587245588</v>
       </c>
       <c r="G50">
-        <v>-8.955904228047411</v>
+        <v>-10.16613185309782</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-20.75590200740416</v>
       </c>
       <c r="E51">
-        <v>-21.47803186346431</v>
+        <v>-19.45744471539933</v>
       </c>
       <c r="F51">
-        <v>-0.705886802603884</v>
+        <v>0.5570313709280058</v>
       </c>
       <c r="G51">
-        <v>-9.601511341866928</v>
+        <v>-9.993262705369546</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-20.99157870881448</v>
       </c>
       <c r="E52">
-        <v>-20.47302948065965</v>
+        <v>-19.04608574652036</v>
       </c>
       <c r="F52">
-        <v>-1.321444962889391</v>
+        <v>0.5069366806111085</v>
       </c>
       <c r="G52">
-        <v>-9.971096178418698</v>
+        <v>-10.38643561930203</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-21.20266751578304</v>
       </c>
       <c r="E53">
-        <v>-20.0079445700827</v>
+        <v>-18.49218025855063</v>
       </c>
       <c r="F53">
-        <v>-1.366593471444173</v>
+        <v>0.3831835608372792</v>
       </c>
       <c r="G53">
-        <v>-11.01342029195313</v>
+        <v>-10.41388498793299</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-21.38519080373723</v>
       </c>
       <c r="E54">
-        <v>-19.93208616523471</v>
+        <v>-17.65293253971987</v>
       </c>
       <c r="F54">
-        <v>-0.8737496582093843</v>
+        <v>0.4725561199253178</v>
       </c>
       <c r="G54">
-        <v>-11.33260339880116</v>
+        <v>-10.46580225487187</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-21.53703764970985</v>
       </c>
       <c r="E55">
-        <v>-20.93339218996027</v>
+        <v>-17.23112409114764</v>
       </c>
       <c r="F55">
-        <v>-1.553361327916363</v>
+        <v>0.5582441008057043</v>
       </c>
       <c r="G55">
-        <v>-10.5452615718747</v>
+        <v>-11.1551197600081</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-21.65222314426799</v>
       </c>
       <c r="E56">
-        <v>-19.90743685602185</v>
+        <v>-18.32937437461735</v>
       </c>
       <c r="F56">
-        <v>-1.694226033129822</v>
+        <v>0.4244312872922777</v>
       </c>
       <c r="G56">
-        <v>-10.40945847047876</v>
+        <v>-10.68125003613661</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-21.73727447140811</v>
       </c>
       <c r="E57">
-        <v>-18.20134332910686</v>
+        <v>-16.5042041258082</v>
       </c>
       <c r="F57">
-        <v>-0.9930768109500558</v>
+        <v>0.3079744276023064</v>
       </c>
       <c r="G57">
-        <v>-10.25690091566935</v>
+        <v>-10.98856991956262</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-21.78833449917922</v>
       </c>
       <c r="E58">
-        <v>-19.32717924219608</v>
+        <v>-16.69391451270372</v>
       </c>
       <c r="F58">
-        <v>-0.6888655092111599</v>
+        <v>0.6985529714918846</v>
       </c>
       <c r="G58">
-        <v>-11.23934368588971</v>
+        <v>-10.7065755640427</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-21.81621478473837</v>
       </c>
       <c r="E59">
-        <v>-18.86055349021762</v>
+        <v>-16.16728731671546</v>
       </c>
       <c r="F59">
-        <v>-1.053021618053642</v>
+        <v>0.6021616553999256</v>
       </c>
       <c r="G59">
-        <v>-11.58877749031497</v>
+        <v>-11.19243513244888</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-21.82770990240682</v>
       </c>
       <c r="E60">
-        <v>-19.57123439927698</v>
+        <v>-16.05706939457716</v>
       </c>
       <c r="F60">
-        <v>-0.6428182220243409</v>
+        <v>0.6133023686001762</v>
       </c>
       <c r="G60">
-        <v>-10.42409561002883</v>
+        <v>-11.46730607135195</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-21.82685072444887</v>
       </c>
       <c r="E61">
-        <v>-17.38756310211996</v>
+        <v>-15.35722006065295</v>
       </c>
       <c r="F61">
-        <v>-0.9620983551875627</v>
+        <v>0.276794678560933</v>
       </c>
       <c r="G61">
-        <v>-9.918304312041796</v>
+        <v>-11.22379278573274</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-21.82558408051085</v>
       </c>
       <c r="E62">
-        <v>-18.54916231792728</v>
+        <v>-15.78898790998213</v>
       </c>
       <c r="F62">
-        <v>-0.9061992944792493</v>
+        <v>0.3806371594410735</v>
       </c>
       <c r="G62">
-        <v>-10.8261163373806</v>
+        <v>-10.90198979668753</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-21.82096858470534</v>
       </c>
       <c r="E63">
-        <v>-19.2091865084577</v>
+        <v>-15.28591772862829</v>
       </c>
       <c r="F63">
-        <v>-1.352700921731822</v>
+        <v>0.4799898889980406</v>
       </c>
       <c r="G63">
-        <v>-11.13855719632208</v>
+        <v>-11.84315016806091</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-21.81773690120405</v>
       </c>
       <c r="E64">
-        <v>-15.6134441269156</v>
+        <v>-15.59115799494657</v>
       </c>
       <c r="F64">
-        <v>-1.403978520699917</v>
+        <v>0.4166148124794616</v>
       </c>
       <c r="G64">
-        <v>-11.24805182447337</v>
+        <v>-11.2783312402411</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-21.80989412601658</v>
       </c>
       <c r="E65">
-        <v>-18.57240784171234</v>
+        <v>-14.63234762849665</v>
       </c>
       <c r="F65">
-        <v>-1.459596764858681</v>
+        <v>0.5376442602328861</v>
       </c>
       <c r="G65">
-        <v>-10.08111165011592</v>
+        <v>-11.2545943504187</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-21.79270000170379</v>
       </c>
       <c r="E66">
-        <v>-18.84551886522174</v>
+        <v>-14.89758416333417</v>
       </c>
       <c r="F66">
-        <v>-1.569390237160533</v>
+        <v>0.4254791720568191</v>
       </c>
       <c r="G66">
-        <v>-11.45578746621596</v>
+        <v>-11.60705270245277</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-21.7673055377063</v>
       </c>
       <c r="E67">
-        <v>-17.9308156030415</v>
+        <v>-14.43814762015899</v>
       </c>
       <c r="F67">
-        <v>-0.8157216932758761</v>
+        <v>0.0550274709530606</v>
       </c>
       <c r="G67">
-        <v>-11.81997980981478</v>
+        <v>-11.59842158083454</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-21.72479593275132</v>
       </c>
       <c r="E68">
-        <v>-15.66215298933319</v>
+        <v>-14.79060159281792</v>
       </c>
       <c r="F68">
-        <v>-1.313365067242485</v>
+        <v>0.3000784295188216</v>
       </c>
       <c r="G68">
-        <v>-11.77639081812156</v>
+        <v>-11.76539697264838</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-21.66841546116733</v>
       </c>
       <c r="E69">
-        <v>-15.81817667917302</v>
+        <v>-14.97898295208949</v>
       </c>
       <c r="F69">
-        <v>-1.060583784073799</v>
+        <v>0.2953733026709204</v>
       </c>
       <c r="G69">
-        <v>-11.13565665908135</v>
+        <v>-11.58524645825549</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-21.590590559588</v>
       </c>
       <c r="E70">
-        <v>-15.74817845550436</v>
+        <v>-14.38195882414539</v>
       </c>
       <c r="F70">
-        <v>-1.932659164514618</v>
+        <v>0.04176199536462932</v>
       </c>
       <c r="G70">
-        <v>-10.48360361686637</v>
+        <v>-11.72709996024134</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-21.49456680943582</v>
       </c>
       <c r="E71">
-        <v>-16.27271658619623</v>
+        <v>-14.45173277440251</v>
       </c>
       <c r="F71">
-        <v>-0.7201405205038551</v>
+        <v>-0.09617443107993315</v>
       </c>
       <c r="G71">
-        <v>-10.09485983113272</v>
+        <v>-11.66319807025695</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-21.38278212901804</v>
       </c>
       <c r="E72">
-        <v>-16.51463699265617</v>
+        <v>-14.50731935477401</v>
       </c>
       <c r="F72">
-        <v>-1.412534727603433</v>
+        <v>0.0505161820774145</v>
       </c>
       <c r="G72">
-        <v>-10.45880937548457</v>
+        <v>-11.71905625615612</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-21.25242156483782</v>
       </c>
       <c r="E73">
-        <v>-18.13612129846175</v>
+        <v>-14.95111490409989</v>
       </c>
       <c r="F73">
-        <v>-1.192268521729433</v>
+        <v>0.1431144038319544</v>
       </c>
       <c r="G73">
-        <v>-11.52807245708241</v>
+        <v>-11.23571866702495</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-21.1132791731139</v>
       </c>
       <c r="E74">
-        <v>-18.7030595635688</v>
+        <v>-15.21129282754377</v>
       </c>
       <c r="F74">
-        <v>-1.677333965051934</v>
+        <v>0.2092611976803005</v>
       </c>
       <c r="G74">
-        <v>-10.89959704926977</v>
+        <v>-11.13929342629677</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-20.96324520579162</v>
       </c>
       <c r="E75">
-        <v>-16.46456172371271</v>
+        <v>-15.5594980650174</v>
       </c>
       <c r="F75">
-        <v>-1.123725260984788</v>
+        <v>0.07233952130416747</v>
       </c>
       <c r="G75">
-        <v>-11.22325497234698</v>
+        <v>-11.02275631461095</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-20.80931873138463</v>
       </c>
       <c r="E76">
-        <v>-17.48844875841137</v>
+        <v>-14.88530727065798</v>
       </c>
       <c r="F76">
-        <v>-1.843442338498305</v>
+        <v>0.1794896732236863</v>
       </c>
       <c r="G76">
-        <v>-12.16898414675481</v>
+        <v>-10.83368488595023</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-20.65235514754216</v>
       </c>
       <c r="E77">
-        <v>-17.60475113514054</v>
+        <v>-14.92219609364511</v>
       </c>
       <c r="F77">
-        <v>-1.760618023729397</v>
+        <v>0.2359130904979719</v>
       </c>
       <c r="G77">
-        <v>-11.0814106079672</v>
+        <v>-10.72136151603447</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-20.48894784873648</v>
       </c>
       <c r="E78">
-        <v>-19.3897099919027</v>
+        <v>-15.98702963879525</v>
       </c>
       <c r="F78">
-        <v>-1.316738179306684</v>
+        <v>-0.2027803456158127</v>
       </c>
       <c r="G78">
-        <v>-9.942272252760512</v>
+        <v>-10.00604491088764</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-20.32355844561588</v>
       </c>
       <c r="E79">
-        <v>-21.55578413267643</v>
+        <v>-17.26222333754795</v>
       </c>
       <c r="F79">
-        <v>-1.979838829941063</v>
+        <v>-0.3019334386287051</v>
       </c>
       <c r="G79">
-        <v>-9.611851195820032</v>
+        <v>-9.988421079525326</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-20.14630526430391</v>
       </c>
       <c r="E80">
-        <v>-19.8191063575654</v>
+        <v>-16.65515674462042</v>
       </c>
       <c r="F80">
-        <v>-2.18335627529786</v>
+        <v>-0.2640770483207677</v>
       </c>
       <c r="G80">
-        <v>-9.298924738384603</v>
+        <v>-9.954470956862489</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-19.95810185306484</v>
       </c>
       <c r="E81">
-        <v>-20.0498297062936</v>
+        <v>-17.20502531118242</v>
       </c>
       <c r="F81">
-        <v>-1.896016332451781</v>
+        <v>-0.01890928995121207</v>
       </c>
       <c r="G81">
-        <v>-10.03410258300833</v>
+        <v>-9.775483529184944</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-19.75085256703658</v>
       </c>
       <c r="E82">
-        <v>-19.04069487822073</v>
+        <v>-17.26628517822364</v>
       </c>
       <c r="F82">
-        <v>-1.790038320407224</v>
+        <v>-0.4016026045335417</v>
       </c>
       <c r="G82">
-        <v>-9.507241270798714</v>
+        <v>-9.357550313550348</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-19.52492628903227</v>
       </c>
       <c r="E83">
-        <v>-19.07878813249206</v>
+        <v>-18.50726887529373</v>
       </c>
       <c r="F83">
-        <v>-1.819895166706326</v>
+        <v>-0.2313515657057705</v>
       </c>
       <c r="G83">
-        <v>-10.31435557188598</v>
+        <v>-9.13318945025155</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-19.28336453546608</v>
       </c>
       <c r="E84">
-        <v>-21.18018431330423</v>
+        <v>-19.13670881762812</v>
       </c>
       <c r="F84">
-        <v>-2.132582323710667</v>
+        <v>-0.2427540430053057</v>
       </c>
       <c r="G84">
-        <v>-10.07169208363118</v>
+        <v>-9.338767311589583</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-19.02193209523632</v>
       </c>
       <c r="E85">
-        <v>-22.20844883273926</v>
+        <v>-20.82836162876668</v>
       </c>
       <c r="F85">
-        <v>-2.038288433882597</v>
+        <v>-0.3602728697056659</v>
       </c>
       <c r="G85">
-        <v>-9.372537292875633</v>
+        <v>-8.563731229293328</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-18.75055508513304</v>
       </c>
       <c r="E86">
-        <v>-23.46012704897079</v>
+        <v>-21.65305649511524</v>
       </c>
       <c r="F86">
-        <v>-2.266109350470128</v>
+        <v>-0.6578622024265828</v>
       </c>
       <c r="G86">
-        <v>-9.673091431693777</v>
+        <v>-8.180614903525818</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-18.47010180649175</v>
       </c>
       <c r="E87">
-        <v>-23.70737602556048</v>
+        <v>-21.67049998267952</v>
       </c>
       <c r="F87">
-        <v>-2.448763534420016</v>
+        <v>-1.010562818455751</v>
       </c>
       <c r="G87">
-        <v>-9.706294881403556</v>
+        <v>-8.399082010910178</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-18.19249355916181</v>
       </c>
       <c r="E88">
-        <v>-26.6098809856075</v>
+        <v>-22.63650371114404</v>
       </c>
       <c r="F88">
-        <v>-2.517627373349544</v>
+        <v>-0.757908275499693</v>
       </c>
       <c r="G88">
-        <v>-8.629207398266153</v>
+        <v>-8.658751889431487</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-17.92803644023509</v>
       </c>
       <c r="E89">
-        <v>-25.71458152673686</v>
+        <v>-23.32856162062287</v>
       </c>
       <c r="F89">
-        <v>-1.3240220138795</v>
+        <v>-1.139133723044262</v>
       </c>
       <c r="G89">
-        <v>-9.016452616604511</v>
+        <v>-7.897537089000587</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-17.68473933365811</v>
       </c>
       <c r="E90">
-        <v>-25.78988340126733</v>
+        <v>-25.25966367748309</v>
       </c>
       <c r="F90">
-        <v>-2.032242180209563</v>
+        <v>-1.091532418609791</v>
       </c>
       <c r="G90">
-        <v>-9.424591623905545</v>
+        <v>-7.940647009061345</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-17.48147161491708</v>
       </c>
       <c r="E91">
-        <v>-28.41527779529914</v>
+        <v>-26.05861694004036</v>
       </c>
       <c r="F91">
-        <v>-2.860017300316067</v>
+        <v>-1.516127041527928</v>
       </c>
       <c r="G91">
-        <v>-9.185072777510744</v>
+        <v>-8.587725277457954</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-17.32411079312827</v>
       </c>
       <c r="E92">
-        <v>-28.77084459984603</v>
+        <v>-27.92316378542021</v>
       </c>
       <c r="F92">
-        <v>-3.372978844295244</v>
+        <v>-1.533903805992006</v>
       </c>
       <c r="G92">
-        <v>-9.095663912871183</v>
+        <v>-8.140743612130336</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-17.22749739583974</v>
       </c>
       <c r="E93">
-        <v>-31.14620944230618</v>
+        <v>-29.76466030794726</v>
       </c>
       <c r="F93">
-        <v>-2.607867233108314</v>
+        <v>-1.575986526789026</v>
       </c>
       <c r="G93">
-        <v>-9.292807763807625</v>
+        <v>-8.161838428426531</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-17.19222747714804</v>
       </c>
       <c r="E94">
-        <v>-32.574195632488</v>
+        <v>-31.30200055231182</v>
       </c>
       <c r="F94">
-        <v>-2.327801184426218</v>
+        <v>-1.71334640952124</v>
       </c>
       <c r="G94">
-        <v>-9.129708022339299</v>
+        <v>-8.696263067716604</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-17.22376926069157</v>
       </c>
       <c r="E95">
-        <v>-34.33052432698246</v>
+        <v>-32.90014381047187</v>
       </c>
       <c r="F95">
-        <v>-3.110832867637909</v>
+        <v>-1.789145340347006</v>
       </c>
       <c r="G95">
-        <v>-10.02575211643365</v>
+        <v>-8.750553501488804</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-17.32162959460035</v>
       </c>
       <c r="E96">
-        <v>-37.12018861193955</v>
+        <v>-34.56631251692129</v>
       </c>
       <c r="F96">
-        <v>-3.347560390540341</v>
+        <v>-1.894030735787271</v>
       </c>
       <c r="G96">
-        <v>-9.924589679644901</v>
+        <v>-9.327567217293707</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-17.47008594926423</v>
       </c>
       <c r="E97">
-        <v>-40.59112906977622</v>
+        <v>-37.10720567333814</v>
       </c>
       <c r="F97">
-        <v>-3.078907587934017</v>
+        <v>-2.383475757568373</v>
       </c>
       <c r="G97">
-        <v>-9.799784339839027</v>
+        <v>-9.453782359178783</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-17.66133023188021</v>
       </c>
       <c r="E98">
-        <v>-40.96680364695226</v>
+        <v>-39.02815312850916</v>
       </c>
       <c r="F98">
-        <v>-3.953087021577946</v>
+        <v>-2.390979109502931</v>
       </c>
       <c r="G98">
-        <v>-9.525429022992705</v>
+        <v>-9.057981730815349</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-17.8640727886252</v>
       </c>
       <c r="E99">
-        <v>-42.55231906607917</v>
+        <v>-41.31544912482632</v>
       </c>
       <c r="F99">
-        <v>-4.158736684629549</v>
+        <v>-2.651590121362878</v>
       </c>
       <c r="G99">
-        <v>-9.056376122891814</v>
+        <v>-9.9059058859786</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-18.06699548474693</v>
       </c>
       <c r="E100">
-        <v>-43.67608460332296</v>
+        <v>-43.70153548232152</v>
       </c>
       <c r="F100">
-        <v>-3.666071798753765</v>
+        <v>-2.716119942040959</v>
       </c>
       <c r="G100">
-        <v>-9.74711126234102</v>
+        <v>-9.532167354782368</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-18.23463190608357</v>
       </c>
       <c r="E101">
-        <v>-45.53257733364114</v>
+        <v>-44.94619269480842</v>
       </c>
       <c r="F101">
-        <v>-4.140211904400743</v>
+        <v>-3.118167232622296</v>
       </c>
       <c r="G101">
-        <v>-10.4993137724434</v>
+        <v>-9.7400961916247</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-18.36817892073235</v>
       </c>
       <c r="E102">
-        <v>-47.6457011449318</v>
+        <v>-47.59363752606658</v>
       </c>
       <c r="F102">
-        <v>-4.129330470197569</v>
+        <v>-3.401338830697488</v>
       </c>
       <c r="G102">
-        <v>-10.89254281738459</v>
+        <v>-10.53542167551079</v>
       </c>
     </row>
   </sheetData>
